--- a/data/trans_orig/IP07C03-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C03-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52308</t>
+          <t>52261</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69116</t>
+          <t>69021</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52388</t>
+          <t>53061</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70782</t>
+          <t>70680</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109300</t>
+          <t>109642</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133672</t>
+          <t>134228</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>57,07%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36052</t>
+          <t>35798</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52496</t>
+          <t>52557</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48215</t>
+          <t>48315</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65899</t>
+          <t>65885</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>90063</t>
+          <t>89405</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113444</t>
+          <t>114342</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,62%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11308</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15744</t>
+          <t>15685</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>577</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5254</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79663</t>
+          <t>78785</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100377</t>
+          <t>99414</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85224</t>
+          <t>85570</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106610</t>
+          <t>107146</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169851</t>
+          <t>169622</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201712</t>
+          <t>201455</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,26%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66316</t>
+          <t>65096</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86934</t>
+          <t>86672</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67169</t>
+          <t>66435</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88978</t>
+          <t>87658</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>139182</t>
+          <t>137617</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>169090</t>
+          <t>168619</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,25%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>16349</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15096</t>
+          <t>14478</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13849</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27420</t>
+          <t>27193</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>679</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>704</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10615</t>
+          <t>9648</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>136044</t>
+          <t>134971</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>163485</t>
+          <t>162810</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>144211</t>
+          <t>144813</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>172413</t>
+          <t>172218</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>288252</t>
+          <t>289017</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>326861</t>
+          <t>327604</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,62%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107415</t>
+          <t>107607</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132846</t>
+          <t>134436</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119161</t>
+          <t>120443</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>148132</t>
+          <t>148098</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>235800</t>
+          <t>235121</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>273946</t>
+          <t>274062</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,7%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>11171</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23550</t>
+          <t>24387</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>8295</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19062</t>
+          <t>19106</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22027</t>
+          <t>21453</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38783</t>
+          <t>38337</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12654</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66669</t>
+          <t>67304</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63510</t>
+          <t>63714</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83181</t>
+          <t>84573</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>117653</t>
+          <t>116723</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>146323</t>
+          <t>145389</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,71%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74768</t>
+          <t>74812</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94993</t>
+          <t>95084</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65495</t>
+          <t>64275</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85592</t>
+          <t>84665</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144119</t>
+          <t>144624</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>173177</t>
+          <t>173051</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,79%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2209</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10390</t>
+          <t>10742</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9887</t>
+          <t>10114</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6366</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17938</t>
+          <t>16740</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>729</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43582</t>
+          <t>43802</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63932</t>
+          <t>64317</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65835</t>
+          <t>64878</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86316</t>
+          <t>86025</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116376</t>
+          <t>115926</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>145845</t>
+          <t>144142</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,31%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86342</t>
+          <t>86395</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107254</t>
+          <t>107003</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71396</t>
+          <t>71942</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>91940</t>
+          <t>93412</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>162260</t>
+          <t>162622</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>193423</t>
+          <t>192832</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>57,93%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14567</t>
+          <t>14754</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15549</t>
+          <t>15383</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25465</t>
+          <t>26762</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>641</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>6417</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7497</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2427</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10856</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98087</t>
+          <t>97841</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>124966</t>
+          <t>124482</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>135170</t>
+          <t>135433</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>165059</t>
+          <t>163032</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>240732</t>
+          <t>242737</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>284972</t>
+          <t>283460</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>165690</t>
+          <t>166414</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194474</t>
+          <t>194426</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>141861</t>
+          <t>143213</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>170151</t>
+          <t>171316</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>314991</t>
+          <t>316568</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>358204</t>
+          <t>357780</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,12%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21644</t>
+          <t>20886</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22352</t>
+          <t>22909</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21551</t>
+          <t>21048</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38520</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>13427</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>92615</t>
+          <t>92313</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114142</t>
+          <t>114692</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96364</t>
+          <t>96452</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>117527</t>
+          <t>117453</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>193668</t>
+          <t>195733</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>224387</t>
+          <t>226684</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>63,06%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56323</t>
+          <t>57069</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76877</t>
+          <t>78896</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50981</t>
+          <t>51606</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72660</t>
+          <t>72032</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114920</t>
+          <t>112425</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>143809</t>
+          <t>143465</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>39,91%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13023</t>
+          <t>13361</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14926</t>
+          <t>14991</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>10775</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24348</t>
+          <t>24813</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>579</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>575</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6165</t>
+          <t>6373</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61180</t>
+          <t>61090</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82328</t>
+          <t>82188</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77128</t>
+          <t>77065</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98728</t>
+          <t>99668</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145957</t>
+          <t>145525</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>177274</t>
+          <t>175431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,31%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67917</t>
+          <t>66866</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89220</t>
+          <t>89142</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59834</t>
+          <t>60057</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81145</t>
+          <t>82240</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>132414</t>
+          <t>133903</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164904</t>
+          <t>164523</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,05%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18559</t>
+          <t>19061</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>5139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14657</t>
+          <t>14789</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14288</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28182</t>
+          <t>28630</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>160790</t>
+          <t>160778</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>190672</t>
+          <t>191182</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>178840</t>
+          <t>179384</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>208334</t>
+          <t>209728</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>350503</t>
+          <t>348197</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>393340</t>
+          <t>392057</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,42%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>128979</t>
+          <t>130300</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>159386</t>
+          <t>161745</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119224</t>
+          <t>118549</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>149101</t>
+          <t>147671</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>257244</t>
+          <t>256623</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>299951</t>
+          <t>299379</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>13006</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28004</t>
+          <t>26796</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12185</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25155</t>
+          <t>25884</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28854</t>
+          <t>28997</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49594</t>
+          <t>48397</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,47 +7037,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>6162</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>3005</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>11596</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>1,67%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>6162</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>2910</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>11248</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -7105,7 +7105,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7077</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C03-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C03-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el/la menor [KIDSCREEN 20] en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>61889</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>53758</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>70754</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>50,12%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>43,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>57,3%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>60804</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>52261</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>69021</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>52051</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>68982</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>54,43%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>46,78%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>61,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>61889</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>53061</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>70680</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>50,12%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109642</t>
+          <t>111256</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>134228</t>
+          <t>134529</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,2%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>56910</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47895</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>65240</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>46,09%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>38,79%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>52,83%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>44088</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>35798</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>52557</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>36067</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>52349</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>39,47%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>32,05%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>47,05%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>56910</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>48315</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>65885</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>46,09%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>89405</t>
+          <t>89083</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>114342</t>
+          <t>112161</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>47,69%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3425</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1272</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7783</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>6166</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2762</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11210</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2837</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>11129</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>5,52%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,04%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3425</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1288</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7435</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15685</t>
+          <t>15769</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4533</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,67%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>654</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3695</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4893</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,59%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1257</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4104</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>578</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>123481</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>123481</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>123481</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>123481</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>123481</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>123481</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>96383</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>85854</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>106424</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>51,93%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>46,25%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>57,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>89172</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>78785</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>99414</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>78528</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>101216</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>49,83%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>44,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>55,56%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>96383</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>85570</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>107146</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>51,93%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169622</t>
+          <t>170974</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201455</t>
+          <t>200851</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,1%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>77003</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>67503</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>87977</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,49%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>36,37%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>47,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>76280</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>65096</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>86672</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>64549</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>86137</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>42,63%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,38%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>48,44%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>77003</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>66435</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>87658</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>41,49%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>137617</t>
+          <t>136911</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>168619</t>
+          <t>168470</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,21%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9445</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5649</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15393</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8,29%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>10468</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6175</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>16349</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6115</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>15832</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>5,85%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,14%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9445</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5464</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>14478</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>13730</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27193</t>
+          <t>27658</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2783</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6921</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2289</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6433</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6330</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2783</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6915</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -1856,107 +1856,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>726</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3623</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3620</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>2,02%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4636</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>185614</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>185614</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>185614</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>185614</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>185614</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>185614</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>158272</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>145021</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>172315</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>51,21%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>46,92%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>55,75%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>149975</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>134971</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>162810</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>136656</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>164260</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>51,6%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>46,44%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>56,02%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>158272</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>144813</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>172218</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>51,21%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>289017</t>
+          <t>289601</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>327604</t>
+          <t>326868</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,5%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>133913</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>120072</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>147270</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>43,32%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>38,85%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>47,65%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>120368</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>107607</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>134436</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>106043</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>133699</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>41,41%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>37,02%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>46,25%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>133913</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>120443</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>148098</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>43,32%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>235121</t>
+          <t>235468</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>274062</t>
+          <t>271873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,33%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>12870</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7976</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>18482</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>16633</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>11171</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>24387</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>10770</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>23190</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>5,72%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>12870</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>8295</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>19106</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21453</t>
+          <t>21392</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38337</t>
+          <t>38326</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4040</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1361</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8105</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>2943</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6968</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7385</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>4040</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1439</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>8808</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>3492</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12075</t>
+          <t>12063</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2538,92 +2538,92 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>726</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3129</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3647</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>309095</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>309095</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>309095</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>432</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>290646</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>290646</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>290646</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>309095</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>309095</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>309095</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el/la menor [KIDSCREEN 20] en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>73559</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>63989</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>84010</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>47,33%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>41,17%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>54,05%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>57552</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>47278</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>67304</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>48908</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>68173</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>38,55%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>31,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>45,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>73559</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>63714</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>84573</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>47,33%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>116723</t>
+          <t>117076</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>145389</t>
+          <t>145898</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,88%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>74532</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>64275</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>84462</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>47,95%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>41,35%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>54,34%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>84444</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>74812</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>95084</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>74688</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>93884</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>56,56%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>50,11%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>63,69%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>74532</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>64275</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>84665</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>47,95%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144624</t>
+          <t>144392</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>173051</t>
+          <t>173184</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,83%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5369</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2549</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10090</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>5354</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2264</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10742</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2353</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10607</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,59%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5369</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>10114</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6298</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16740</t>
+          <t>17328</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -3342,67 +3342,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1144</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4007</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1345</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4664</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4567</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,9%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1144</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3801</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>735</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -3455,102 +3455,102 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4112</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>594</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3554</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3438</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>823</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1417</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4115</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4467</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1417</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4884</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>149289</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>149289</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>149289</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>76538</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>65792</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>87584</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>44,67%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>38,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>51,12%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>54072</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>43802</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>64317</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>44694</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>65425</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>33,48%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27,12%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>39,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>76538</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>64878</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>86025</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>44,67%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>115926</t>
+          <t>116658</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>144142</t>
+          <t>145151</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,61%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>81753</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>70852</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>92811</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>47,71%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>41,35%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>54,17%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>96494</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>86395</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>107003</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>85182</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>106362</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>59,75%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>53,49%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>66,25%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>81753</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>71942</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>93412</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>47,71%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>162622</t>
+          <t>163151</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192832</t>
+          <t>193809</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,23%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,11%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>9,51%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>8727</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4987</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>14754</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4637</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>13759</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>5,4%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,14%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5536</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>15383</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>12774</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26762</t>
+          <t>25985</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3375</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1148</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7373</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2215</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6417</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5702</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3375</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7632</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2427</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>11345</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>171339</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>171339</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>171339</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>161508</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>161508</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>161508</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>171339</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>171339</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>171339</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>150097</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>135334</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>164015</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>45,93%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>41,42%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>50,19%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>111624</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>97841</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>124482</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>98556</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>125722</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>35,92%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>31,48%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>40,05%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>150097</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>135433</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>163032</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>45,93%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>242737</t>
+          <t>242066</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>283460</t>
+          <t>284343</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,6%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>156285</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>141797</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>170867</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>47,83%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>43,39%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>52,29%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>180939</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>166414</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>194426</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>164975</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>193793</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>58,22%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>53,54%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>62,56%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>156285</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>143213</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>171316</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>47,83%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>316568</t>
+          <t>314446</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>357780</t>
+          <t>356943</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>15042</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>10191</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>22855</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>14081</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>9055</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>20886</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>8694</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>21809</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>4,53%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,72%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>15042</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>9687</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>22909</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21048</t>
+          <t>21017</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38520</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4519</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1764</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8960</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>3560</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1258</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7828</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7870</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>4519</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>8848</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13427</t>
+          <t>14028</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -4819,102 +4819,102 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4144</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>594</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3566</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>823</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1417</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4077</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>5415</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1417</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>4790</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>326766</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>326766</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>326766</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>442</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>310798</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>310798</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>310798</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>326766</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>326766</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>326766</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el/la menor [KIDSCREEN 20] en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>106524</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>95256</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>117064</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>59,64%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>53,33%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>65,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>103490</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>92313</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>114692</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>91570</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>113467</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>57,21%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>51,03%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>63,41%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>106524</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>96452</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>117453</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>59,64%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>195733</t>
+          <t>194333</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>226684</t>
+          <t>226780</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,08%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>61661</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>51160</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>72849</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34,52%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>28,64%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>40,79%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>66977</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>57069</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>78896</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>57245</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>78780</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>37,03%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,55%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>43,62%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>61661</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>51606</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>72032</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>34,52%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112425</t>
+          <t>113396</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>143465</t>
+          <t>144181</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,11%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9233</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5360</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>14600</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>7412</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3821</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13361</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3755</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>4,1%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,39%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>9233</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>5757</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>14991</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24813</t>
+          <t>24658</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1355</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4828</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,75%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3121</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>583</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -5726,72 +5726,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2901</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1653</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6454</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5807</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3084</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>180887</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>180887</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>180887</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>87929</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>75727</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>98678</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>51,54%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>44,39%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>57,84%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>71937</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>61090</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>61556</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>83296</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>43,65%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,07%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>49,87%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>87929</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>77065</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>99668</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>51,54%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145525</t>
+          <t>144375</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175431</t>
+          <t>175593</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,35%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>71437</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>61364</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>82594</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,88%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>35,97%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>48,42%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>78033</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>66866</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>89142</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>67134</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>88362</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>47,35%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>40,57%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>54,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>71437</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>60057</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>82240</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>41,88%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133903</t>
+          <t>133607</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164523</t>
+          <t>164395</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,01%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8896</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5243</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15407</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5,21%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>9,03%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>12086</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7338</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19061</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7653</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>18670</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>7,33%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,57%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>8896</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5139</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>14789</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>14648</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28630</t>
+          <t>29141</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1438</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5046</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2751</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7159</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>989</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6734</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,67%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1438</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5079</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8471</t>
+          <t>9526</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -6408,107 +6408,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4497</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>891</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4464</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>5743</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4899</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>194453</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>178748</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>210612</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>55,68%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>51,19%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>60,31%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>175427</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>160778</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>191182</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>158063</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>189184</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>50,75%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>46,51%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>55,3%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>194453</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>179384</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>209728</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>55,68%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>348197</t>
+          <t>346752</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>392057</t>
+          <t>391369</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,32%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>133098</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>118302</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>149094</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>38,11%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>33,88%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>42,7%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>145010</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>130300</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>161745</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>130633</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>160909</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>41,95%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>37,69%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>46,79%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>133098</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>118549</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>147671</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>38,11%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>256623</t>
+          <t>257622</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>299379</t>
+          <t>301458</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,38%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>18129</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>12063</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>25535</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>19498</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>13006</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>26796</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>13307</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>26509</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>5,64%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>18129</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>12013</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>25884</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28997</t>
+          <t>28571</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48397</t>
+          <t>48548</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5622</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>4105</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1739</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>9029</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1566</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>9084</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2056</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5522</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11596</t>
+          <t>12188</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -7095,67 +7095,67 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5587</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>1653</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6023</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5983</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1467</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5721</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>493</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>345694</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>345694</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>345694</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
